--- a/data/nzd0509/nzd0509.xlsx
+++ b/data/nzd0509/nzd0509.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q436"/>
+  <dimension ref="A1:Q437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25242,6 +25242,63 @@
         <v>331.15</v>
       </c>
       <c r="Q436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>386.84</v>
+      </c>
+      <c r="C437" t="n">
+        <v>316.2</v>
+      </c>
+      <c r="D437" t="n">
+        <v>326.61</v>
+      </c>
+      <c r="E437" t="n">
+        <v>333.4</v>
+      </c>
+      <c r="F437" t="n">
+        <v>342.22</v>
+      </c>
+      <c r="G437" t="n">
+        <v>340.53</v>
+      </c>
+      <c r="H437" t="n">
+        <v>331.35</v>
+      </c>
+      <c r="I437" t="n">
+        <v>322.06</v>
+      </c>
+      <c r="J437" t="n">
+        <v>310.88</v>
+      </c>
+      <c r="K437" t="n">
+        <v>300.94</v>
+      </c>
+      <c r="L437" t="n">
+        <v>314.84</v>
+      </c>
+      <c r="M437" t="n">
+        <v>321.77</v>
+      </c>
+      <c r="N437" t="n">
+        <v>335.26</v>
+      </c>
+      <c r="O437" t="n">
+        <v>338.99</v>
+      </c>
+      <c r="P437" t="n">
+        <v>331.1</v>
+      </c>
+      <c r="Q437" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25258,7 +25315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B509"/>
+  <dimension ref="A1:B510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30351,6 +30408,16 @@
       </c>
       <c r="B509" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>
@@ -30519,28 +30586,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2220289642997613</v>
+        <v>0.2217679502492022</v>
       </c>
       <c r="J2" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K2" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02130302128125738</v>
+        <v>0.0213438063100998</v>
       </c>
       <c r="M2" t="n">
-        <v>7.344075412359201</v>
+        <v>7.327931785331261</v>
       </c>
       <c r="N2" t="n">
-        <v>95.45451494725445</v>
+        <v>95.23215587945428</v>
       </c>
       <c r="O2" t="n">
-        <v>9.770082647923427</v>
+        <v>9.758696423162997</v>
       </c>
       <c r="P2" t="n">
-        <v>381.53580780001</v>
+        <v>381.5391173803247</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30601,28 +30668,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2252715219961469</v>
+        <v>-0.2293557996312907</v>
       </c>
       <c r="J3" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K3" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01657382311055644</v>
+        <v>0.01722132973460233</v>
       </c>
       <c r="M3" t="n">
-        <v>8.971944794622168</v>
+        <v>8.969717176788398</v>
       </c>
       <c r="N3" t="n">
-        <v>126.7065638810739</v>
+        <v>126.5733494898255</v>
       </c>
       <c r="O3" t="n">
-        <v>11.25640101813515</v>
+        <v>11.25048218921418</v>
       </c>
       <c r="P3" t="n">
-        <v>330.4855083515912</v>
+        <v>330.5372931333737</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30679,28 +30746,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05688425777402704</v>
+        <v>-0.0544132349576168</v>
       </c>
       <c r="J4" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K4" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001172577997870738</v>
+        <v>0.001077133678137443</v>
       </c>
       <c r="M4" t="n">
-        <v>8.398664334997033</v>
+        <v>8.39040457118916</v>
       </c>
       <c r="N4" t="n">
-        <v>117.0236406687429</v>
+        <v>116.8137604243694</v>
       </c>
       <c r="O4" t="n">
-        <v>10.81774656149528</v>
+        <v>10.80804147032983</v>
       </c>
       <c r="P4" t="n">
-        <v>322.9961278752812</v>
+        <v>322.9650179765384</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30757,28 +30824,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1431886716352726</v>
+        <v>0.1442644284518811</v>
       </c>
       <c r="J5" t="n">
+        <v>436</v>
+      </c>
+      <c r="K5" t="n">
         <v>435</v>
       </c>
-      <c r="K5" t="n">
-        <v>434</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.008916573458684462</v>
+        <v>0.009087497769164954</v>
       </c>
       <c r="M5" t="n">
-        <v>7.918034288255362</v>
+        <v>7.904847639604323</v>
       </c>
       <c r="N5" t="n">
-        <v>98.01575838076444</v>
+        <v>97.80198437744508</v>
       </c>
       <c r="O5" t="n">
-        <v>9.900290823039716</v>
+        <v>9.889488580176685</v>
       </c>
       <c r="P5" t="n">
-        <v>327.383370105068</v>
+        <v>327.3699123996404</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30835,28 +30902,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.258078622053247</v>
+        <v>0.2634511643664004</v>
       </c>
       <c r="J6" t="n">
+        <v>436</v>
+      </c>
+      <c r="K6" t="n">
         <v>435</v>
       </c>
-      <c r="K6" t="n">
-        <v>434</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03282519508775983</v>
+        <v>0.03418842906003017</v>
       </c>
       <c r="M6" t="n">
-        <v>7.442726828548843</v>
+        <v>7.451897293332003</v>
       </c>
       <c r="N6" t="n">
-        <v>84.40498238257845</v>
+        <v>84.49901767712149</v>
       </c>
       <c r="O6" t="n">
-        <v>9.18721842466905</v>
+        <v>9.192334723949161</v>
       </c>
       <c r="P6" t="n">
-        <v>324.2015546329801</v>
+        <v>324.1343441903118</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30913,28 +30980,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5535822478133435</v>
+        <v>0.5578218797814507</v>
       </c>
       <c r="J7" t="n">
+        <v>436</v>
+      </c>
+      <c r="K7" t="n">
         <v>435</v>
       </c>
-      <c r="K7" t="n">
-        <v>434</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1587732829915822</v>
+        <v>0.1610565569900689</v>
       </c>
       <c r="M7" t="n">
-        <v>6.731975073615079</v>
+        <v>6.734859034889111</v>
       </c>
       <c r="N7" t="n">
-        <v>69.83390123309697</v>
+        <v>69.85275189057691</v>
       </c>
       <c r="O7" t="n">
-        <v>8.356668070056209</v>
+        <v>8.35779587514417</v>
       </c>
       <c r="P7" t="n">
-        <v>317.1144003864196</v>
+        <v>317.0613626391635</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30991,28 +31058,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7599202272146012</v>
+        <v>0.7585289976171252</v>
       </c>
       <c r="J8" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K8" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1717547759219535</v>
+        <v>0.1718234124565156</v>
       </c>
       <c r="M8" t="n">
-        <v>8.617997402357165</v>
+        <v>8.606189554542986</v>
       </c>
       <c r="N8" t="n">
-        <v>119.4552386678824</v>
+        <v>119.199261742121</v>
       </c>
       <c r="O8" t="n">
-        <v>10.92955802710624</v>
+        <v>10.91784144151769</v>
       </c>
       <c r="P8" t="n">
-        <v>314.2814726940833</v>
+        <v>314.2989089324579</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31069,28 +31136,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2374972796736482</v>
+        <v>0.2376412219896559</v>
       </c>
       <c r="J9" t="n">
+        <v>436</v>
+      </c>
+      <c r="K9" t="n">
         <v>435</v>
       </c>
-      <c r="K9" t="n">
-        <v>434</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01019241096356538</v>
+        <v>0.01024821965896994</v>
       </c>
       <c r="M9" t="n">
-        <v>12.94890489852705</v>
+        <v>12.91995046535707</v>
       </c>
       <c r="N9" t="n">
-        <v>235.8059058376645</v>
+        <v>235.2640304033329</v>
       </c>
       <c r="O9" t="n">
-        <v>15.35597296942348</v>
+        <v>15.33831902143559</v>
       </c>
       <c r="P9" t="n">
-        <v>315.5187681504927</v>
+        <v>315.516968141616</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31147,28 +31214,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1626487534809415</v>
+        <v>-0.1677548806215442</v>
       </c>
       <c r="J10" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K10" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004994616468851021</v>
+        <v>0.005328277813498872</v>
       </c>
       <c r="M10" t="n">
-        <v>12.01068344465226</v>
+        <v>12.00700787777712</v>
       </c>
       <c r="N10" t="n">
-        <v>224.5667327650388</v>
+        <v>224.3060509518032</v>
       </c>
       <c r="O10" t="n">
-        <v>14.98555079952148</v>
+        <v>14.97685050175113</v>
       </c>
       <c r="P10" t="n">
-        <v>325.7501054023178</v>
+        <v>325.8142909508114</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31225,28 +31292,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2694747120446594</v>
+        <v>-0.2770662786619591</v>
       </c>
       <c r="J11" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K11" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L11" t="n">
-        <v>0.009878733036521758</v>
+        <v>0.01046323425146956</v>
       </c>
       <c r="M11" t="n">
-        <v>14.64549339231542</v>
+        <v>14.64037825130863</v>
       </c>
       <c r="N11" t="n">
-        <v>309.0038354898721</v>
+        <v>308.8558931566351</v>
       </c>
       <c r="O11" t="n">
-        <v>17.5785049276061</v>
+        <v>17.5742963772845</v>
       </c>
       <c r="P11" t="n">
-        <v>323.7207522437089</v>
+        <v>323.8163292117541</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31303,28 +31370,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1052347233993833</v>
+        <v>-0.1086462886926742</v>
       </c>
       <c r="J12" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K12" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002121299513527464</v>
+        <v>0.002269388075945011</v>
       </c>
       <c r="M12" t="n">
-        <v>12.41245417532398</v>
+        <v>12.39791974327224</v>
       </c>
       <c r="N12" t="n">
-        <v>221.1742613731873</v>
+        <v>220.7785529517377</v>
       </c>
       <c r="O12" t="n">
-        <v>14.87192863663578</v>
+        <v>14.85861881036517</v>
       </c>
       <c r="P12" t="n">
-        <v>324.6597843844316</v>
+        <v>324.7027356069472</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31381,28 +31448,28 @@
         <v>0.1389</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4340240363732534</v>
+        <v>-0.4347968454474995</v>
       </c>
       <c r="J13" t="n">
+        <v>436</v>
+      </c>
+      <c r="K13" t="n">
         <v>435</v>
       </c>
-      <c r="K13" t="n">
-        <v>434</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.0477460268827774</v>
+        <v>0.04810315538960275</v>
       </c>
       <c r="M13" t="n">
-        <v>9.539817825817734</v>
+        <v>9.521754011505593</v>
       </c>
       <c r="N13" t="n">
-        <v>161.7359873514411</v>
+        <v>161.3701503413903</v>
       </c>
       <c r="O13" t="n">
-        <v>12.71754643598525</v>
+        <v>12.70315513332772</v>
       </c>
       <c r="P13" t="n">
-        <v>334.7901466171074</v>
+        <v>334.7998106494243</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31459,28 +31526,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.606667254174725</v>
+        <v>-0.5995309260091375</v>
       </c>
       <c r="J14" t="n">
+        <v>436</v>
+      </c>
+      <c r="K14" t="n">
         <v>435</v>
       </c>
-      <c r="K14" t="n">
-        <v>434</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.09437531034985203</v>
+        <v>0.09245211086664851</v>
       </c>
       <c r="M14" t="n">
-        <v>9.596610352646785</v>
+        <v>9.615202695571597</v>
       </c>
       <c r="N14" t="n">
-        <v>152.0388285771873</v>
+        <v>152.198374246898</v>
       </c>
       <c r="O14" t="n">
-        <v>12.33040261212858</v>
+        <v>12.33687052079651</v>
       </c>
       <c r="P14" t="n">
-        <v>336.2729707947008</v>
+        <v>336.1837305045509</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31537,28 +31604,28 @@
         <v>0.089</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3282465899326486</v>
+        <v>-0.322761181766107</v>
       </c>
       <c r="J15" t="n">
+        <v>436</v>
+      </c>
+      <c r="K15" t="n">
         <v>435</v>
       </c>
-      <c r="K15" t="n">
-        <v>434</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.04565415821959162</v>
+        <v>0.04425872787245</v>
       </c>
       <c r="M15" t="n">
-        <v>7.611298043764863</v>
+        <v>7.621849267336719</v>
       </c>
       <c r="N15" t="n">
-        <v>96.95929252275242</v>
+        <v>97.03716961625166</v>
       </c>
       <c r="O15" t="n">
-        <v>9.846790975884094</v>
+        <v>9.850744622425843</v>
       </c>
       <c r="P15" t="n">
-        <v>336.139081685226</v>
+        <v>336.0704862668239</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31615,28 +31682,28 @@
         <v>0.035</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4028935480431637</v>
+        <v>-0.3994357071973996</v>
       </c>
       <c r="J16" t="n">
+        <v>436</v>
+      </c>
+      <c r="K16" t="n">
         <v>435</v>
       </c>
-      <c r="K16" t="n">
-        <v>434</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.06675912296573272</v>
+        <v>0.0658823997016752</v>
       </c>
       <c r="M16" t="n">
-        <v>7.442194620842998</v>
+        <v>7.442795911745535</v>
       </c>
       <c r="N16" t="n">
-        <v>97.68486974633417</v>
+        <v>97.5798237861577</v>
       </c>
       <c r="O16" t="n">
-        <v>9.883565639299118</v>
+        <v>9.878250036628842</v>
       </c>
       <c r="P16" t="n">
-        <v>334.4551376626305</v>
+        <v>334.4118971174638</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31674,7 +31741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q436"/>
+  <dimension ref="A1:Q437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69477,6 +69544,93 @@
         </is>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>-45.89907307652666,170.6522909971317</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>-45.898197155523995,170.65213747744218</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>-45.89789398223343,170.65133756833345</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-45.89756349859906,170.65056069379534</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>-45.89734905522113,170.64971437774986</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>-45.89713016472238,170.6488761073657</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>-45.89684664746333,170.64806928845218</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>-45.89655934042744,170.64724693908684</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>-45.896343206721376,170.6463723571499</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>-45.89616479710043,170.6454966908113</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>-45.89619871589954,170.64457839377974</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>-45.89617079472839,170.64367513187008</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>-45.896198820766486,170.64275940177689</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>-45.89610619527426,170.6418701073264</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>-45.89591166519817,170.64101241264459</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0509/nzd0509.xlsx
+++ b/data/nzd0509/nzd0509.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q437"/>
+  <dimension ref="A1:Q438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25301,6 +25301,63 @@
       <c r="Q437" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>392.3</v>
+      </c>
+      <c r="C438" t="n">
+        <v>329.13</v>
+      </c>
+      <c r="D438" t="n">
+        <v>336.93</v>
+      </c>
+      <c r="E438" t="n">
+        <v>344.73</v>
+      </c>
+      <c r="F438" t="n">
+        <v>351.3</v>
+      </c>
+      <c r="G438" t="n">
+        <v>349.45</v>
+      </c>
+      <c r="H438" t="n">
+        <v>342.77</v>
+      </c>
+      <c r="I438" t="n">
+        <v>334.49</v>
+      </c>
+      <c r="J438" t="n">
+        <v>320.65</v>
+      </c>
+      <c r="K438" t="n">
+        <v>310.46</v>
+      </c>
+      <c r="L438" t="n">
+        <v>321.44</v>
+      </c>
+      <c r="M438" t="n">
+        <v>332.32</v>
+      </c>
+      <c r="N438" t="n">
+        <v>343.2</v>
+      </c>
+      <c r="O438" t="n">
+        <v>345.51</v>
+      </c>
+      <c r="P438" t="n">
+        <v>334.38</v>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -25315,7 +25372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B510"/>
+  <dimension ref="A1:B513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30418,6 +30475,36 @@
       </c>
       <c r="B510" t="n">
         <v>-0.66</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>-0.17</v>
       </c>
     </row>
   </sheetData>
@@ -30586,28 +30673,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2217679502492022</v>
+        <v>0.2241673780048473</v>
       </c>
       <c r="J2" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K2" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0213438063100998</v>
+        <v>0.02187859788400026</v>
       </c>
       <c r="M2" t="n">
-        <v>7.327931785331261</v>
+        <v>7.324365489948754</v>
       </c>
       <c r="N2" t="n">
-        <v>95.23215587945428</v>
+        <v>95.06595100615694</v>
       </c>
       <c r="O2" t="n">
-        <v>9.758696423162997</v>
+        <v>9.750176973068589</v>
       </c>
       <c r="P2" t="n">
-        <v>381.5391173803247</v>
+        <v>381.5085836148969</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30668,28 +30755,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2293557996312907</v>
+        <v>-0.2270854631428464</v>
       </c>
       <c r="J3" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K3" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01722132973460233</v>
+        <v>0.01695399711007506</v>
       </c>
       <c r="M3" t="n">
-        <v>8.969717176788398</v>
+        <v>8.960021855556915</v>
       </c>
       <c r="N3" t="n">
-        <v>126.5733494898255</v>
+        <v>126.3286886033595</v>
       </c>
       <c r="O3" t="n">
-        <v>11.25048218921418</v>
+        <v>11.23960357856804</v>
       </c>
       <c r="P3" t="n">
-        <v>330.5372931333737</v>
+        <v>330.5084041674357</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30746,28 +30833,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0544132349576168</v>
+        <v>-0.04694398716964417</v>
       </c>
       <c r="J4" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K4" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001077133678137443</v>
+        <v>0.0008017310734809158</v>
       </c>
       <c r="M4" t="n">
-        <v>8.39040457118916</v>
+        <v>8.404508929393799</v>
       </c>
       <c r="N4" t="n">
-        <v>116.8137604243694</v>
+        <v>117.086946650496</v>
       </c>
       <c r="O4" t="n">
-        <v>10.80804147032983</v>
+        <v>10.82067219032607</v>
       </c>
       <c r="P4" t="n">
-        <v>322.9650179765384</v>
+        <v>322.8706458951128</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30824,28 +30911,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1442644284518811</v>
+        <v>0.1507654615308218</v>
       </c>
       <c r="J5" t="n">
+        <v>437</v>
+      </c>
+      <c r="K5" t="n">
         <v>436</v>
       </c>
-      <c r="K5" t="n">
-        <v>435</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.009087497769164954</v>
+        <v>0.009917381338829689</v>
       </c>
       <c r="M5" t="n">
-        <v>7.904847639604323</v>
+        <v>7.916667305513117</v>
       </c>
       <c r="N5" t="n">
-        <v>97.80198437744508</v>
+        <v>97.99615444024482</v>
       </c>
       <c r="O5" t="n">
-        <v>9.889488580176685</v>
+        <v>9.899300704607615</v>
       </c>
       <c r="P5" t="n">
-        <v>327.3699123996404</v>
+        <v>327.288291633687</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30902,28 +30989,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2634511643664004</v>
+        <v>0.2731482440571038</v>
       </c>
       <c r="J6" t="n">
+        <v>437</v>
+      </c>
+      <c r="K6" t="n">
         <v>436</v>
       </c>
-      <c r="K6" t="n">
-        <v>435</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03418842906003017</v>
+        <v>0.03642411079037278</v>
       </c>
       <c r="M6" t="n">
-        <v>7.451897293332003</v>
+        <v>7.481797589621788</v>
       </c>
       <c r="N6" t="n">
-        <v>84.49901767712149</v>
+        <v>85.23631762007605</v>
       </c>
       <c r="O6" t="n">
-        <v>9.192334723949161</v>
+        <v>9.23235168416347</v>
       </c>
       <c r="P6" t="n">
-        <v>324.1343441903118</v>
+        <v>324.012596913801</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30980,28 +31067,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5578218797814507</v>
+        <v>0.5663014157315155</v>
       </c>
       <c r="J7" t="n">
+        <v>437</v>
+      </c>
+      <c r="K7" t="n">
         <v>436</v>
       </c>
-      <c r="K7" t="n">
-        <v>435</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1610565569900689</v>
+        <v>0.1643754343158833</v>
       </c>
       <c r="M7" t="n">
-        <v>6.734859034889111</v>
+        <v>6.755675299542646</v>
       </c>
       <c r="N7" t="n">
-        <v>69.85275189057691</v>
+        <v>70.40450787880036</v>
       </c>
       <c r="O7" t="n">
-        <v>8.35779587514417</v>
+        <v>8.390739411923144</v>
       </c>
       <c r="P7" t="n">
-        <v>317.0613626391635</v>
+        <v>316.9549016796868</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31058,28 +31145,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7585289976171252</v>
+        <v>0.7626033827939197</v>
       </c>
       <c r="J8" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K8" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1718234124565156</v>
+        <v>0.1737800603484688</v>
       </c>
       <c r="M8" t="n">
-        <v>8.606189554542986</v>
+        <v>8.601796921391594</v>
       </c>
       <c r="N8" t="n">
-        <v>119.199261742121</v>
+        <v>119.0891745245837</v>
       </c>
       <c r="O8" t="n">
-        <v>10.91784144151769</v>
+        <v>10.91279865683335</v>
       </c>
       <c r="P8" t="n">
-        <v>314.2989089324579</v>
+        <v>314.247660789284</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31136,28 +31223,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2376412219896559</v>
+        <v>0.2437329245856567</v>
       </c>
       <c r="J9" t="n">
+        <v>437</v>
+      </c>
+      <c r="K9" t="n">
         <v>436</v>
       </c>
-      <c r="K9" t="n">
-        <v>435</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01024821965896994</v>
+        <v>0.01080432200891646</v>
       </c>
       <c r="M9" t="n">
-        <v>12.91995046535707</v>
+        <v>12.92445956227331</v>
       </c>
       <c r="N9" t="n">
-        <v>235.2640304033329</v>
+        <v>235.0924564377276</v>
       </c>
       <c r="O9" t="n">
-        <v>15.33831902143559</v>
+        <v>15.33272501669966</v>
       </c>
       <c r="P9" t="n">
-        <v>315.516968141616</v>
+        <v>315.4405163146417</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31214,28 +31301,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1677548806215442</v>
+        <v>-0.1681134408089202</v>
       </c>
       <c r="J10" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K10" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005328277813498872</v>
+        <v>0.005374234670953881</v>
       </c>
       <c r="M10" t="n">
-        <v>12.00700787777712</v>
+        <v>11.98107470543704</v>
       </c>
       <c r="N10" t="n">
-        <v>224.3060509518032</v>
+        <v>223.7916609515952</v>
       </c>
       <c r="O10" t="n">
-        <v>14.97685050175113</v>
+        <v>14.95966780886512</v>
       </c>
       <c r="P10" t="n">
-        <v>325.8142909508114</v>
+        <v>325.8188142867983</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31292,28 +31379,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2770662786619591</v>
+        <v>-0.2800015946146492</v>
       </c>
       <c r="J11" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K11" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01046323425146956</v>
+        <v>0.0107272492416749</v>
       </c>
       <c r="M11" t="n">
-        <v>14.64037825130863</v>
+        <v>14.61764084453354</v>
       </c>
       <c r="N11" t="n">
-        <v>308.8558931566351</v>
+        <v>308.2295426675066</v>
       </c>
       <c r="O11" t="n">
-        <v>17.5742963772845</v>
+        <v>17.55646726045723</v>
       </c>
       <c r="P11" t="n">
-        <v>323.8163292117541</v>
+        <v>323.8534161961413</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31370,28 +31457,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1086462886926742</v>
+        <v>-0.1088396640392126</v>
       </c>
       <c r="J12" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K12" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002269388075945011</v>
+        <v>0.002287427490802907</v>
       </c>
       <c r="M12" t="n">
-        <v>12.39791974327224</v>
+        <v>12.37020604442756</v>
       </c>
       <c r="N12" t="n">
-        <v>220.7785529517377</v>
+        <v>220.2713791483901</v>
       </c>
       <c r="O12" t="n">
-        <v>14.85861881036517</v>
+        <v>14.84154234398804</v>
       </c>
       <c r="P12" t="n">
-        <v>324.7027356069472</v>
+        <v>324.7051788561828</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31448,28 +31535,28 @@
         <v>0.1389</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4347968454474995</v>
+        <v>-0.4304915555677621</v>
       </c>
       <c r="J13" t="n">
+        <v>437</v>
+      </c>
+      <c r="K13" t="n">
         <v>436</v>
       </c>
-      <c r="K13" t="n">
-        <v>435</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.04810315538960275</v>
+        <v>0.04734446599061015</v>
       </c>
       <c r="M13" t="n">
-        <v>9.521754011505593</v>
+        <v>9.519555126808219</v>
       </c>
       <c r="N13" t="n">
-        <v>161.3701503413903</v>
+        <v>161.1838591032484</v>
       </c>
       <c r="O13" t="n">
-        <v>12.70315513332772</v>
+        <v>12.69582053682425</v>
       </c>
       <c r="P13" t="n">
-        <v>334.7998106494243</v>
+        <v>334.7457785833849</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31526,28 +31613,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5995309260091375</v>
+        <v>-0.5885899072821817</v>
       </c>
       <c r="J14" t="n">
+        <v>437</v>
+      </c>
+      <c r="K14" t="n">
         <v>436</v>
       </c>
-      <c r="K14" t="n">
-        <v>435</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.09245211086664851</v>
+        <v>0.08912790532433212</v>
       </c>
       <c r="M14" t="n">
-        <v>9.615202695571597</v>
+        <v>9.654791145081703</v>
       </c>
       <c r="N14" t="n">
-        <v>152.198374246898</v>
+        <v>153.0364640902303</v>
       </c>
       <c r="O14" t="n">
-        <v>12.33687052079651</v>
+        <v>12.37079076252728</v>
       </c>
       <c r="P14" t="n">
-        <v>336.1837305045509</v>
+        <v>336.0464189964047</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31604,28 +31691,28 @@
         <v>0.089</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.322761181766107</v>
+        <v>-0.3141555972527795</v>
       </c>
       <c r="J15" t="n">
+        <v>437</v>
+      </c>
+      <c r="K15" t="n">
         <v>436</v>
       </c>
-      <c r="K15" t="n">
-        <v>435</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.04425872787245</v>
+        <v>0.04189898157517058</v>
       </c>
       <c r="M15" t="n">
-        <v>7.621849267336719</v>
+        <v>7.648301546547608</v>
       </c>
       <c r="N15" t="n">
-        <v>97.03716961625166</v>
+        <v>97.5490495584673</v>
       </c>
       <c r="O15" t="n">
-        <v>9.850744622425843</v>
+        <v>9.876692237711334</v>
       </c>
       <c r="P15" t="n">
-        <v>336.0704862668239</v>
+        <v>335.962484825871</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31682,28 +31769,28 @@
         <v>0.035</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3994357071973996</v>
+        <v>-0.3944022808159963</v>
       </c>
       <c r="J16" t="n">
+        <v>437</v>
+      </c>
+      <c r="K16" t="n">
         <v>436</v>
       </c>
-      <c r="K16" t="n">
-        <v>435</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.0658823997016752</v>
+        <v>0.06444532433407479</v>
       </c>
       <c r="M16" t="n">
-        <v>7.442795911745535</v>
+        <v>7.451196702834557</v>
       </c>
       <c r="N16" t="n">
-        <v>97.5798237861577</v>
+        <v>97.60727742684885</v>
       </c>
       <c r="O16" t="n">
-        <v>9.878250036628842</v>
+        <v>9.87963953931766</v>
       </c>
       <c r="P16" t="n">
-        <v>334.4118971174638</v>
+        <v>334.3487268236529</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31741,7 +31828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q437"/>
+  <dimension ref="A1:Q438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69631,6 +69718,93 @@
         </is>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>-45.89911166023045,170.65224745211594</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>-45.898288526897474,170.6520343588072</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>-45.8979669093192,170.65125526459042</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-45.897648558273,170.65048024137292</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>-45.89742340360607,170.64966589824274</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>-45.897205372446464,170.6488360020187</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>-45.89694293332237,170.64801794216018</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>-45.896666780547235,170.64720250211653</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>-45.89642961044534,170.64634923630908</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>-45.89624929894074,170.6454766755074</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>-45.89625729901214,170.64456451695483</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>-45.89626441197069,170.64365271790035</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>-45.89626890479344,170.64273960129455</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>-45.8961634127281,170.64185159598279</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>-45.895940449384945,170.64100309993427</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0509/nzd0509.xlsx
+++ b/data/nzd0509/nzd0509.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q438"/>
+  <dimension ref="A1:Q439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25356,6 +25356,63 @@
         <v>334.38</v>
       </c>
       <c r="Q438" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:48+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>392.96</v>
+      </c>
+      <c r="C439" t="n">
+        <v>336.66</v>
+      </c>
+      <c r="D439" t="n">
+        <v>337.97</v>
+      </c>
+      <c r="E439" t="n">
+        <v>346.68</v>
+      </c>
+      <c r="F439" t="n">
+        <v>354.64</v>
+      </c>
+      <c r="G439" t="n">
+        <v>350.87</v>
+      </c>
+      <c r="H439" t="n">
+        <v>345.44</v>
+      </c>
+      <c r="I439" t="n">
+        <v>341.33</v>
+      </c>
+      <c r="J439" t="n">
+        <v>323.41</v>
+      </c>
+      <c r="K439" t="n">
+        <v>315.18</v>
+      </c>
+      <c r="L439" t="n">
+        <v>326.25</v>
+      </c>
+      <c r="M439" t="n">
+        <v>333.04</v>
+      </c>
+      <c r="N439" t="n">
+        <v>342.84</v>
+      </c>
+      <c r="O439" t="n">
+        <v>346.28</v>
+      </c>
+      <c r="P439" t="n">
+        <v>336.87</v>
+      </c>
+      <c r="Q439" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25372,7 +25429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B513"/>
+  <dimension ref="A1:B514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30505,6 +30562,16 @@
       </c>
       <c r="B513" t="n">
         <v>-0.17</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -30673,28 +30740,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2241673780048473</v>
+        <v>0.2268751371531126</v>
       </c>
       <c r="J2" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K2" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02187859788400026</v>
+        <v>0.02247875950926581</v>
       </c>
       <c r="M2" t="n">
-        <v>7.324365489948754</v>
+        <v>7.322441947258791</v>
       </c>
       <c r="N2" t="n">
-        <v>95.06595100615694</v>
+        <v>94.91530119149603</v>
       </c>
       <c r="O2" t="n">
-        <v>9.750176973068589</v>
+        <v>9.74244841872391</v>
       </c>
       <c r="P2" t="n">
-        <v>381.5085836148969</v>
+        <v>381.4739999802426</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30755,28 +30822,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2270854631428464</v>
+        <v>-0.2211129163345402</v>
       </c>
       <c r="J3" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K3" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01695399711007506</v>
+        <v>0.01611527373652499</v>
       </c>
       <c r="M3" t="n">
-        <v>8.960021855556915</v>
+        <v>8.968262481151427</v>
       </c>
       <c r="N3" t="n">
-        <v>126.3286886033595</v>
+        <v>126.3765960806057</v>
       </c>
       <c r="O3" t="n">
-        <v>11.23960357856804</v>
+        <v>11.24173456725454</v>
       </c>
       <c r="P3" t="n">
-        <v>330.5084041674357</v>
+        <v>330.4321294787071</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30833,28 +30900,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04694398716964417</v>
+        <v>-0.03899798173823064</v>
       </c>
       <c r="J4" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K4" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008017310734809158</v>
+        <v>0.0005530048373537655</v>
       </c>
       <c r="M4" t="n">
-        <v>8.404508929393799</v>
+        <v>8.421827231963702</v>
       </c>
       <c r="N4" t="n">
-        <v>117.086946650496</v>
+        <v>117.4264290065111</v>
       </c>
       <c r="O4" t="n">
-        <v>10.82067219032607</v>
+        <v>10.83634758608781</v>
       </c>
       <c r="P4" t="n">
-        <v>322.8706458951128</v>
+        <v>322.7698866793747</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30911,28 +30978,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1507654615308218</v>
+        <v>0.1581774522769655</v>
       </c>
       <c r="J5" t="n">
+        <v>438</v>
+      </c>
+      <c r="K5" t="n">
         <v>437</v>
       </c>
-      <c r="K5" t="n">
-        <v>436</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.009917381338829689</v>
+        <v>0.01089365822545774</v>
       </c>
       <c r="M5" t="n">
-        <v>7.916667305513117</v>
+        <v>7.932703909765713</v>
       </c>
       <c r="N5" t="n">
-        <v>97.99615444024482</v>
+        <v>98.31141542558096</v>
       </c>
       <c r="O5" t="n">
-        <v>9.899300704607615</v>
+        <v>9.915211315225761</v>
       </c>
       <c r="P5" t="n">
-        <v>327.288291633687</v>
+        <v>327.1948932750922</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30989,28 +31056,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2731482440571038</v>
+        <v>0.2844057102257596</v>
       </c>
       <c r="J6" t="n">
+        <v>438</v>
+      </c>
+      <c r="K6" t="n">
         <v>437</v>
       </c>
-      <c r="K6" t="n">
-        <v>436</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03642411079037278</v>
+        <v>0.03898633013401209</v>
       </c>
       <c r="M6" t="n">
-        <v>7.481797589621788</v>
+        <v>7.518584658821259</v>
       </c>
       <c r="N6" t="n">
-        <v>85.23631762007605</v>
+        <v>86.28581164241778</v>
       </c>
       <c r="O6" t="n">
-        <v>9.23235168416347</v>
+        <v>9.289015644427442</v>
       </c>
       <c r="P6" t="n">
-        <v>324.012596913801</v>
+        <v>323.8707417903801</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31067,28 +31134,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5663014157315155</v>
+        <v>0.5754122149054249</v>
       </c>
       <c r="J7" t="n">
+        <v>438</v>
+      </c>
+      <c r="K7" t="n">
         <v>437</v>
       </c>
-      <c r="K7" t="n">
-        <v>436</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1643754343158833</v>
+        <v>0.1678074222912239</v>
       </c>
       <c r="M7" t="n">
-        <v>6.755675299542646</v>
+        <v>6.778749705244108</v>
       </c>
       <c r="N7" t="n">
-        <v>70.40450787880036</v>
+        <v>71.05855658234245</v>
       </c>
       <c r="O7" t="n">
-        <v>8.390739411923144</v>
+        <v>8.429623750935889</v>
       </c>
       <c r="P7" t="n">
-        <v>316.9549016796868</v>
+        <v>316.8400966674472</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31145,28 +31212,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7626033827939197</v>
+        <v>0.767917092433909</v>
       </c>
       <c r="J8" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K8" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1737800603484688</v>
+        <v>0.1760835739616226</v>
       </c>
       <c r="M8" t="n">
-        <v>8.601796921391594</v>
+        <v>8.601934562883724</v>
       </c>
       <c r="N8" t="n">
-        <v>119.0891745245837</v>
+        <v>119.0925593003153</v>
       </c>
       <c r="O8" t="n">
-        <v>10.91279865683335</v>
+        <v>10.91295373857671</v>
       </c>
       <c r="P8" t="n">
-        <v>314.247660789284</v>
+        <v>314.180579626478</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31223,28 +31290,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2437329245856567</v>
+        <v>0.2530794475388491</v>
       </c>
       <c r="J9" t="n">
+        <v>438</v>
+      </c>
+      <c r="K9" t="n">
         <v>437</v>
       </c>
-      <c r="K9" t="n">
-        <v>436</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01080432200891646</v>
+        <v>0.01164750436732886</v>
       </c>
       <c r="M9" t="n">
-        <v>12.92445956227331</v>
+        <v>12.94685569287968</v>
       </c>
       <c r="N9" t="n">
-        <v>235.0924564377276</v>
+        <v>235.4137134647902</v>
       </c>
       <c r="O9" t="n">
-        <v>15.33272501669966</v>
+        <v>15.34319762842121</v>
       </c>
       <c r="P9" t="n">
-        <v>315.4405163146417</v>
+        <v>315.3227863554877</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31301,28 +31368,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1681134408089202</v>
+        <v>-0.1671230802579235</v>
       </c>
       <c r="J10" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K10" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005374234670953881</v>
+        <v>0.005334589231593023</v>
       </c>
       <c r="M10" t="n">
-        <v>11.98107470543704</v>
+        <v>11.95834894552062</v>
       </c>
       <c r="N10" t="n">
-        <v>223.7916609515952</v>
+        <v>223.2878808143398</v>
       </c>
       <c r="O10" t="n">
-        <v>14.95966780886512</v>
+        <v>14.94282037683448</v>
       </c>
       <c r="P10" t="n">
-        <v>325.8188142867983</v>
+        <v>325.8062752040296</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31379,28 +31446,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2800015946146492</v>
+        <v>-0.2806159070303014</v>
       </c>
       <c r="J11" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K11" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0107272492416749</v>
+        <v>0.0108210161467186</v>
       </c>
       <c r="M11" t="n">
-        <v>14.61764084453354</v>
+        <v>14.58636718408277</v>
       </c>
       <c r="N11" t="n">
-        <v>308.2295426675066</v>
+        <v>307.5262283528822</v>
       </c>
       <c r="O11" t="n">
-        <v>17.55646726045723</v>
+        <v>17.53642575763038</v>
       </c>
       <c r="P11" t="n">
-        <v>323.8534161961413</v>
+        <v>323.8612059765227</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31457,28 +31524,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1088396640392126</v>
+        <v>-0.1066901840468395</v>
       </c>
       <c r="J12" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K12" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002287427490802907</v>
+        <v>0.002207451566366592</v>
       </c>
       <c r="M12" t="n">
-        <v>12.37020604442756</v>
+        <v>12.35333165001414</v>
       </c>
       <c r="N12" t="n">
-        <v>220.2713791483901</v>
+        <v>219.8106628399873</v>
       </c>
       <c r="O12" t="n">
-        <v>14.84154234398804</v>
+        <v>14.8260130459941</v>
       </c>
       <c r="P12" t="n">
-        <v>324.7051788561828</v>
+        <v>324.6779224038502</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31535,28 +31602,28 @@
         <v>0.1389</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4304915555677621</v>
+        <v>-0.4258345779205982</v>
       </c>
       <c r="J13" t="n">
+        <v>438</v>
+      </c>
+      <c r="K13" t="n">
         <v>437</v>
       </c>
-      <c r="K13" t="n">
-        <v>436</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.04734446599061015</v>
+        <v>0.046508813846593</v>
       </c>
       <c r="M13" t="n">
-        <v>9.519555126808219</v>
+        <v>9.51876319748329</v>
       </c>
       <c r="N13" t="n">
-        <v>161.1838591032484</v>
+        <v>161.0283294644594</v>
       </c>
       <c r="O13" t="n">
-        <v>12.69582053682425</v>
+        <v>12.68969382863351</v>
       </c>
       <c r="P13" t="n">
-        <v>334.7457785833849</v>
+        <v>334.6871187169374</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31613,28 +31680,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5885899072821817</v>
+        <v>-0.5778357988898039</v>
       </c>
       <c r="J14" t="n">
+        <v>438</v>
+      </c>
+      <c r="K14" t="n">
         <v>437</v>
       </c>
-      <c r="K14" t="n">
-        <v>436</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.08912790532433212</v>
+        <v>0.08594068550060596</v>
       </c>
       <c r="M14" t="n">
-        <v>9.654791145081703</v>
+        <v>9.692604803070051</v>
       </c>
       <c r="N14" t="n">
-        <v>153.0364640902303</v>
+        <v>153.8237785102334</v>
       </c>
       <c r="O14" t="n">
-        <v>12.37079076252728</v>
+        <v>12.40257144749561</v>
       </c>
       <c r="P14" t="n">
-        <v>336.0464189964047</v>
+        <v>335.9109589169597</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31691,28 +31758,28 @@
         <v>0.089</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3141555972527795</v>
+        <v>-0.3051985296179585</v>
       </c>
       <c r="J15" t="n">
+        <v>438</v>
+      </c>
+      <c r="K15" t="n">
         <v>437</v>
       </c>
-      <c r="K15" t="n">
-        <v>436</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.04189898157517058</v>
+        <v>0.03949729508212851</v>
       </c>
       <c r="M15" t="n">
-        <v>7.648301546547608</v>
+        <v>7.676038489309035</v>
       </c>
       <c r="N15" t="n">
-        <v>97.5490495584673</v>
+        <v>98.11493779492025</v>
       </c>
       <c r="O15" t="n">
-        <v>9.876692237711334</v>
+        <v>9.905298470764031</v>
       </c>
       <c r="P15" t="n">
-        <v>335.962484825871</v>
+        <v>335.8496604940773</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31769,28 +31836,28 @@
         <v>0.035</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3944022808159963</v>
+        <v>-0.3881730649980469</v>
       </c>
       <c r="J16" t="n">
+        <v>438</v>
+      </c>
+      <c r="K16" t="n">
         <v>437</v>
       </c>
-      <c r="K16" t="n">
-        <v>436</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.06444532433407479</v>
+        <v>0.06258033783129735</v>
       </c>
       <c r="M16" t="n">
-        <v>7.451196702834557</v>
+        <v>7.465283239304439</v>
       </c>
       <c r="N16" t="n">
-        <v>97.60727742684885</v>
+        <v>97.76557751337548</v>
       </c>
       <c r="O16" t="n">
-        <v>9.87963953931766</v>
+        <v>9.887647723972345</v>
       </c>
       <c r="P16" t="n">
-        <v>334.3487268236529</v>
+        <v>334.270262850742</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31828,7 +31895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q438"/>
+  <dimension ref="A1:Q439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69805,6 +69872,93 @@
         </is>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:48+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>-45.89911632419342,170.6522421884286</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>-45.89834173848605,170.6519743058025</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>-45.897974258556836,170.65124697040272</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>-45.897663197839876,170.65046639472612</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>-45.89745075201477,170.64964806543915</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>-45.89721734497496,170.64882961752488</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>-45.89696544498588,170.64800593735268</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>-45.8967259028562,170.64717804919408</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>-45.896454019274934,170.64634270471674</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>-45.89629119480898,170.645466751929</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>-45.89629999367272,170.6445544036731</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>-45.89627080101446,170.64365118822363</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>-45.89626572718023,170.64274049905057</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>-45.89617017000381,170.64184940982452</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>-45.8959623007943,170.6409960302175</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0509/nzd0509.xlsx
+++ b/data/nzd0509/nzd0509.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q439"/>
+  <dimension ref="A1:Q445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25415,6 +25415,348 @@
       <c r="Q439" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>398.85</v>
+      </c>
+      <c r="C440" t="n">
+        <v>341.51</v>
+      </c>
+      <c r="D440" t="n">
+        <v>343.99</v>
+      </c>
+      <c r="E440" t="n">
+        <v>350.76</v>
+      </c>
+      <c r="F440" t="n">
+        <v>355.23</v>
+      </c>
+      <c r="G440" t="n">
+        <v>352.79</v>
+      </c>
+      <c r="H440" t="n">
+        <v>354.14</v>
+      </c>
+      <c r="I440" t="n">
+        <v>353.41</v>
+      </c>
+      <c r="J440" t="n">
+        <v>346.76</v>
+      </c>
+      <c r="K440" t="n">
+        <v>338</v>
+      </c>
+      <c r="L440" t="n">
+        <v>340.4</v>
+      </c>
+      <c r="M440" t="n">
+        <v>344.65</v>
+      </c>
+      <c r="N440" t="n">
+        <v>350.88</v>
+      </c>
+      <c r="O440" t="n">
+        <v>352.13</v>
+      </c>
+      <c r="P440" t="n">
+        <v>344.64</v>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>397.27</v>
+      </c>
+      <c r="C441" t="n">
+        <v>340.92</v>
+      </c>
+      <c r="D441" t="n">
+        <v>343.86</v>
+      </c>
+      <c r="E441" t="n">
+        <v>350.29</v>
+      </c>
+      <c r="F441" t="n">
+        <v>353.33</v>
+      </c>
+      <c r="G441" t="n">
+        <v>351.61</v>
+      </c>
+      <c r="H441" t="n">
+        <v>353.32</v>
+      </c>
+      <c r="I441" t="n">
+        <v>352.7</v>
+      </c>
+      <c r="J441" t="n">
+        <v>346.82</v>
+      </c>
+      <c r="K441" t="n">
+        <v>338.82</v>
+      </c>
+      <c r="L441" t="n">
+        <v>341.25</v>
+      </c>
+      <c r="M441" t="n">
+        <v>343.5</v>
+      </c>
+      <c r="N441" t="n">
+        <v>347.65</v>
+      </c>
+      <c r="O441" t="n">
+        <v>349.74</v>
+      </c>
+      <c r="P441" t="n">
+        <v>341.84</v>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>395.86</v>
+      </c>
+      <c r="C442" t="n">
+        <v>341.65</v>
+      </c>
+      <c r="D442" t="n">
+        <v>344.65</v>
+      </c>
+      <c r="E442" t="n">
+        <v>350.26</v>
+      </c>
+      <c r="F442" t="n">
+        <v>353.24</v>
+      </c>
+      <c r="G442" t="n">
+        <v>351.46</v>
+      </c>
+      <c r="H442" t="n">
+        <v>353.31</v>
+      </c>
+      <c r="I442" t="n">
+        <v>352.82</v>
+      </c>
+      <c r="J442" t="n">
+        <v>348.14</v>
+      </c>
+      <c r="K442" t="n">
+        <v>341.44</v>
+      </c>
+      <c r="L442" t="n">
+        <v>342.07</v>
+      </c>
+      <c r="M442" t="n">
+        <v>344.21</v>
+      </c>
+      <c r="N442" t="n">
+        <v>348.31</v>
+      </c>
+      <c r="O442" t="n">
+        <v>349.34</v>
+      </c>
+      <c r="P442" t="n">
+        <v>341.28</v>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>392.3</v>
+      </c>
+      <c r="C443" t="n">
+        <v>341.55</v>
+      </c>
+      <c r="D443" t="n">
+        <v>341.54</v>
+      </c>
+      <c r="E443" t="n">
+        <v>348.59</v>
+      </c>
+      <c r="F443" t="n">
+        <v>350.63</v>
+      </c>
+      <c r="G443" t="n">
+        <v>349.59</v>
+      </c>
+      <c r="H443" t="n">
+        <v>350.48</v>
+      </c>
+      <c r="I443" t="n">
+        <v>352.71</v>
+      </c>
+      <c r="J443" t="n">
+        <v>347.4</v>
+      </c>
+      <c r="K443" t="n">
+        <v>342.74</v>
+      </c>
+      <c r="L443" t="n">
+        <v>342.32</v>
+      </c>
+      <c r="M443" t="n">
+        <v>345.18</v>
+      </c>
+      <c r="N443" t="n">
+        <v>347.06</v>
+      </c>
+      <c r="O443" t="n">
+        <v>347.41</v>
+      </c>
+      <c r="P443" t="n">
+        <v>341.13</v>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>392.22</v>
+      </c>
+      <c r="C444" t="n">
+        <v>343.28</v>
+      </c>
+      <c r="D444" t="n">
+        <v>342.28</v>
+      </c>
+      <c r="E444" t="n">
+        <v>349.18</v>
+      </c>
+      <c r="F444" t="n">
+        <v>351.52</v>
+      </c>
+      <c r="G444" t="n">
+        <v>349.87</v>
+      </c>
+      <c r="H444" t="n">
+        <v>351.03</v>
+      </c>
+      <c r="I444" t="n">
+        <v>351.46</v>
+      </c>
+      <c r="J444" t="n">
+        <v>348.7</v>
+      </c>
+      <c r="K444" t="n">
+        <v>345.61</v>
+      </c>
+      <c r="L444" t="n">
+        <v>344.82</v>
+      </c>
+      <c r="M444" t="n">
+        <v>346.86</v>
+      </c>
+      <c r="N444" t="n">
+        <v>348.41</v>
+      </c>
+      <c r="O444" t="n">
+        <v>347.99</v>
+      </c>
+      <c r="P444" t="n">
+        <v>341.35</v>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>392.26</v>
+      </c>
+      <c r="C445" t="n">
+        <v>345.03</v>
+      </c>
+      <c r="D445" t="n">
+        <v>342.45</v>
+      </c>
+      <c r="E445" t="n">
+        <v>349.52</v>
+      </c>
+      <c r="F445" t="n">
+        <v>351.69</v>
+      </c>
+      <c r="G445" t="n">
+        <v>350.47</v>
+      </c>
+      <c r="H445" t="n">
+        <v>351.51</v>
+      </c>
+      <c r="I445" t="n">
+        <v>349.56</v>
+      </c>
+      <c r="J445" t="n">
+        <v>349.55</v>
+      </c>
+      <c r="K445" t="n">
+        <v>347.73</v>
+      </c>
+      <c r="L445" t="n">
+        <v>346.61</v>
+      </c>
+      <c r="M445" t="n">
+        <v>347.94</v>
+      </c>
+      <c r="N445" t="n">
+        <v>349.65</v>
+      </c>
+      <c r="O445" t="n">
+        <v>348.14</v>
+      </c>
+      <c r="P445" t="n">
+        <v>339.8</v>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -25429,7 +25771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B514"/>
+  <dimension ref="A1:B520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30572,6 +30914,66 @@
       </c>
       <c r="B514" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -30740,28 +31142,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2268751371531126</v>
+        <v>0.2479093998000374</v>
       </c>
       <c r="J2" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="K2" t="n">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02247875950926581</v>
+        <v>0.02720891256853142</v>
       </c>
       <c r="M2" t="n">
-        <v>7.322441947258791</v>
+        <v>7.335771007537247</v>
       </c>
       <c r="N2" t="n">
-        <v>94.91530119149603</v>
+        <v>94.40495826654281</v>
       </c>
       <c r="O2" t="n">
-        <v>9.74244841872391</v>
+        <v>9.716221398596412</v>
       </c>
       <c r="P2" t="n">
-        <v>381.4739999802426</v>
+        <v>381.2028830385921</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30822,28 +31224,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2211129163345402</v>
+        <v>-0.1694695489243973</v>
       </c>
       <c r="J3" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="K3" t="n">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01611527373652499</v>
+        <v>0.009472652177566987</v>
       </c>
       <c r="M3" t="n">
-        <v>8.968262481151427</v>
+        <v>9.094400302148676</v>
       </c>
       <c r="N3" t="n">
-        <v>126.3765960806057</v>
+        <v>128.8406967982501</v>
       </c>
       <c r="O3" t="n">
-        <v>11.24173456725454</v>
+        <v>11.35080159276208</v>
       </c>
       <c r="P3" t="n">
-        <v>330.4321294787071</v>
+        <v>329.7663077323488</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30900,28 +31302,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03899798173823064</v>
+        <v>0.02251220307232516</v>
       </c>
       <c r="J4" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="K4" t="n">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005530048373537655</v>
+        <v>0.0001801051016170341</v>
       </c>
       <c r="M4" t="n">
-        <v>8.421827231963702</v>
+        <v>8.603152994151175</v>
       </c>
       <c r="N4" t="n">
-        <v>117.4264290065111</v>
+        <v>121.8173534646594</v>
       </c>
       <c r="O4" t="n">
-        <v>10.83634758608781</v>
+        <v>11.03708990018018</v>
       </c>
       <c r="P4" t="n">
-        <v>322.7698866793747</v>
+        <v>321.9825901614314</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30978,28 +31380,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1581774522769655</v>
+        <v>0.2103515423657865</v>
       </c>
       <c r="J5" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="K5" t="n">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01089365822545774</v>
+        <v>0.01878320485768836</v>
       </c>
       <c r="M5" t="n">
-        <v>7.932703909765713</v>
+        <v>8.059662743870868</v>
       </c>
       <c r="N5" t="n">
-        <v>98.31141542558096</v>
+        <v>101.3662198321104</v>
       </c>
       <c r="O5" t="n">
-        <v>9.915211315225761</v>
+        <v>10.06807925237532</v>
       </c>
       <c r="P5" t="n">
-        <v>327.1948932750922</v>
+        <v>326.5312092671405</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31056,28 +31458,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2844057102257596</v>
+        <v>0.3445227759761889</v>
       </c>
       <c r="J6" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="K6" t="n">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03898633013401209</v>
+        <v>0.05412667951072447</v>
       </c>
       <c r="M6" t="n">
-        <v>7.518584658821259</v>
+        <v>7.701200709853221</v>
       </c>
       <c r="N6" t="n">
-        <v>86.28581164241778</v>
+        <v>90.96284550752621</v>
       </c>
       <c r="O6" t="n">
-        <v>9.289015644427442</v>
+        <v>9.537444390796006</v>
       </c>
       <c r="P6" t="n">
-        <v>323.8707417903801</v>
+        <v>323.1060409702259</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31134,28 +31536,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5754122149054249</v>
+        <v>0.6287693200500141</v>
       </c>
       <c r="J7" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="K7" t="n">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1678074222912239</v>
+        <v>0.1883892861169073</v>
       </c>
       <c r="M7" t="n">
-        <v>6.778749705244108</v>
+        <v>6.914631913845724</v>
       </c>
       <c r="N7" t="n">
-        <v>71.05855658234245</v>
+        <v>74.69315906806344</v>
       </c>
       <c r="O7" t="n">
-        <v>8.429623750935889</v>
+        <v>8.642520411781707</v>
       </c>
       <c r="P7" t="n">
-        <v>316.8400966674472</v>
+        <v>316.161377334096</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31212,28 +31614,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.767917092433909</v>
+        <v>0.8181438509710763</v>
       </c>
       <c r="J8" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="K8" t="n">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1760835739616226</v>
+        <v>0.1941020568688703</v>
       </c>
       <c r="M8" t="n">
-        <v>8.601934562883724</v>
+        <v>8.672779081644634</v>
       </c>
       <c r="N8" t="n">
-        <v>119.0925593003153</v>
+        <v>121.5487125240328</v>
       </c>
       <c r="O8" t="n">
-        <v>10.91295373857671</v>
+        <v>11.02491326605488</v>
       </c>
       <c r="P8" t="n">
-        <v>314.180579626478</v>
+        <v>313.5405117631227</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31290,28 +31692,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2530794475388491</v>
+        <v>0.3384094792143355</v>
       </c>
       <c r="J9" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="K9" t="n">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01164750436732886</v>
+        <v>0.0201868678324314</v>
       </c>
       <c r="M9" t="n">
-        <v>12.94685569287968</v>
+        <v>13.24050998221128</v>
       </c>
       <c r="N9" t="n">
-        <v>235.4137134647902</v>
+        <v>243.9786268501325</v>
       </c>
       <c r="O9" t="n">
-        <v>15.34319762842121</v>
+        <v>15.61981519897507</v>
       </c>
       <c r="P9" t="n">
-        <v>315.3227863554877</v>
+        <v>314.2377522330119</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31368,28 +31770,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1671230802579235</v>
+        <v>-0.09102740660659084</v>
       </c>
       <c r="J10" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="K10" t="n">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005334589231593023</v>
+        <v>0.001566658163098755</v>
       </c>
       <c r="M10" t="n">
-        <v>11.95834894552062</v>
+        <v>12.15763733528371</v>
       </c>
       <c r="N10" t="n">
-        <v>223.2878808143398</v>
+        <v>229.4575996797502</v>
       </c>
       <c r="O10" t="n">
-        <v>14.94282037683448</v>
+        <v>15.14785792380395</v>
       </c>
       <c r="P10" t="n">
-        <v>325.8062752040296</v>
+        <v>324.8336752129368</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31446,28 +31848,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2806159070303014</v>
+        <v>-0.2058011941472183</v>
       </c>
       <c r="J11" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="K11" t="n">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0108210161467186</v>
+        <v>0.005837240006467459</v>
       </c>
       <c r="M11" t="n">
-        <v>14.58636718408277</v>
+        <v>14.80901207442903</v>
       </c>
       <c r="N11" t="n">
-        <v>307.5262283528822</v>
+        <v>312.3367784959221</v>
       </c>
       <c r="O11" t="n">
-        <v>17.53642575763038</v>
+        <v>17.67305232538856</v>
       </c>
       <c r="P11" t="n">
-        <v>323.8612059765227</v>
+        <v>322.9034639897259</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31524,28 +31926,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1066901840468395</v>
+        <v>-0.04607694589443075</v>
       </c>
       <c r="J12" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="K12" t="n">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002207451566366592</v>
+        <v>0.0004126514981743767</v>
       </c>
       <c r="M12" t="n">
-        <v>12.35333165001414</v>
+        <v>12.50352073478986</v>
       </c>
       <c r="N12" t="n">
-        <v>219.8106628399873</v>
+        <v>222.6804549507441</v>
       </c>
       <c r="O12" t="n">
-        <v>14.8260130459941</v>
+        <v>14.92248152790762</v>
       </c>
       <c r="P12" t="n">
-        <v>324.6779224038502</v>
+        <v>323.9020061414553</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31602,28 +32004,28 @@
         <v>0.1389</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4258345779205982</v>
+        <v>-0.3631144081398365</v>
       </c>
       <c r="J13" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="K13" t="n">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="L13" t="n">
-        <v>0.046508813846593</v>
+        <v>0.03384375677352991</v>
       </c>
       <c r="M13" t="n">
-        <v>9.51876319748329</v>
+        <v>9.668431049279475</v>
       </c>
       <c r="N13" t="n">
-        <v>161.0283294644594</v>
+        <v>165.2145113284057</v>
       </c>
       <c r="O13" t="n">
-        <v>12.68969382863351</v>
+        <v>12.8535797087195</v>
       </c>
       <c r="P13" t="n">
-        <v>334.6871187169374</v>
+        <v>333.8895107979206</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31680,28 +32082,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5778357988898039</v>
+        <v>-0.4977898671701079</v>
       </c>
       <c r="J14" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="K14" t="n">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08594068550060596</v>
+        <v>0.06288378525365856</v>
       </c>
       <c r="M14" t="n">
-        <v>9.692604803070051</v>
+        <v>9.997977882621111</v>
       </c>
       <c r="N14" t="n">
-        <v>153.8237785102334</v>
+        <v>162.0836872128351</v>
       </c>
       <c r="O14" t="n">
-        <v>12.40257144749561</v>
+        <v>12.73120918109647</v>
       </c>
       <c r="P14" t="n">
-        <v>335.9109589169597</v>
+        <v>334.8930913155332</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31758,28 +32160,28 @@
         <v>0.089</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3051985296179585</v>
+        <v>-0.2443384331761229</v>
       </c>
       <c r="J15" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="K15" t="n">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03949729508212851</v>
+        <v>0.02486014467353181</v>
       </c>
       <c r="M15" t="n">
-        <v>7.676038489309035</v>
+        <v>7.878094314013512</v>
       </c>
       <c r="N15" t="n">
-        <v>98.11493779492025</v>
+        <v>102.7872511503044</v>
       </c>
       <c r="O15" t="n">
-        <v>9.905298470764031</v>
+        <v>10.13840476358605</v>
       </c>
       <c r="P15" t="n">
-        <v>335.8496604940773</v>
+        <v>335.0757997313097</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31836,28 +32238,28 @@
         <v>0.035</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3881730649980469</v>
+        <v>-0.3376996656131883</v>
       </c>
       <c r="J16" t="n">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="K16" t="n">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="L16" t="n">
-        <v>0.06258033783129735</v>
+        <v>0.04740979894280339</v>
       </c>
       <c r="M16" t="n">
-        <v>7.465283239304439</v>
+        <v>7.614072689403083</v>
       </c>
       <c r="N16" t="n">
-        <v>97.76557751337548</v>
+        <v>100.575380588188</v>
       </c>
       <c r="O16" t="n">
-        <v>9.887647723972345</v>
+        <v>10.02872776518477</v>
       </c>
       <c r="P16" t="n">
-        <v>334.270262850742</v>
+        <v>333.6284758071542</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31895,7 +32297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q439"/>
+  <dimension ref="A1:Q445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69959,6 +70361,528 @@
         </is>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>-45.89915794651799,170.65219521396745</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>-45.89837601153626,170.6519356261831</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>-45.89801679932337,170.65119895977293</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>-45.897693828312256,170.6504374232567</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>-45.897455583020765,170.64964491533127</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>-45.89723353318182,170.64882098496537</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>-45.897038797586745,170.64796682049467</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>-45.896830317677626,170.64713486319854</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>-45.89666052148767,170.64628744625364</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>-45.89649375066021,170.64541877372244</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>-45.89642559230178,170.6445246524456</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>-45.896373824340394,170.64362652213387</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>-45.896336693872485,170.64272044914009</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>-45.89622150774589,170.64183280068164</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>-45.89603048771831,170.6409739692563</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>-45.89914678127848,170.6522078149334</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>-45.89837184223812,170.65194033154143</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>-45.89801588066919,170.65119999654812</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-45.89769029980236,170.65044076065803</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>-45.89744002554347,170.64965505974448</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>-45.897223584179784,170.6488262903932</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>-45.897031883894016,170.6479705073755</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>-45.89682418071436,170.64713740145297</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>-45.8966610521143,170.6462873042613</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>-45.89650102917834,170.64541704969574</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>-45.89643313709534,170.64452286526478</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>-45.89636361961858,170.64362896537716</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>-45.89630818362239,170.6427285040236</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>-45.89620053386536,170.6418395863012</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>-45.896005915854495,170.6409819191588</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>-45.89913681736093,170.65221906009495</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>-45.8983770008612,170.6519345096573</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>-45.89802146325991,170.65119369614456</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-45.89769007457832,170.65044097368363</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>-45.89743928861032,170.6496555402692</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>-45.89722231947611,170.64882696481186</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>-45.897031799580695,170.64797055233745</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>-45.896825217947594,170.64713697245224</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>-45.896672725899805,170.6462841804292</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>-45.896524284931104,170.64541154121684</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>-45.89644041560203,170.6445211411604</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>-45.89636991992509,170.64362745694012</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>-45.89631400924632,170.6427268581348</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>-45.89619702359242,170.6418407219692</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>-45.89600100148164,170.64098350913844</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>-45.89911166023045,170.65224745211594</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>-45.89837629420053,170.65193530717573</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>-45.89799948622336,170.65121849899162</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-45.89767753710615,170.65045283210597</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>-45.89741791754765,170.64966947547964</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>-45.89720655283662,170.6488353725617</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>-45.89700793890836,170.64798327656516</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>-45.89682426715047,170.6471373657029</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>-45.89666618150492,170.6462859316686</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>-45.89653582404491,170.64540880800024</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>-45.89644263465894,170.64452061551873</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>-45.89637852738607,170.6436253961171</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>-45.896302975867634,170.64272997534815</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>-45.896180086525206,170.64184620156524</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>-45.89599968513177,170.64098393502576</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>-45.899111094901585,170.6522480901386</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>-45.898388519429396,170.65192151010388</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>-45.89800471548661,170.65121259735136</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-45.897681966512636,170.6504486426041</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>-45.89742520499837,170.6496647236275</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>-45.89720891361692,170.6488341136476</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>-45.89701257614164,170.6479808036596</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>-45.89681346263752,170.64714183445926</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>-45.89667767841483,170.64628285516667</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>-45.8965612988573,170.64540277389474</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>-45.89646482522779,170.64451535909956</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>-45.89639343515338,170.64362182685497</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>-45.89631489191661,170.6427266087577</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>-45.896185176421085,170.64184455484764</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>-45.89600161577826,170.640983310391</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>-45.899111377566015,170.65224777112726</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>-45.898400885988536,170.6519075535221</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>-45.89800591680379,170.65121124156897</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-45.8976845190519,170.65044622831456</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>-45.89742659698331,170.6496638159702</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>-45.897213972431764,170.64883141597414</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>-45.89701662318153,170.64797864548711</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>-45.896797039777404,170.64714862696547</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>-45.89668519562509,170.646280843607</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>-45.89658011648841,170.64539831664223</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>-45.89648071367485,170.64451159550063</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>-45.89640301871797,170.64361953232824</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>-45.89632583702814,170.64272351648066</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>-45.89618649277348,170.64184412897234</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>-45.89598801349609,170.64098771122596</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0509/nzd0509.xlsx
+++ b/data/nzd0509/nzd0509.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q445"/>
+  <dimension ref="A1:Q449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25755,6 +25755,234 @@
         <v>339.8</v>
       </c>
       <c r="Q445" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>390.28</v>
+      </c>
+      <c r="C446" t="n">
+        <v>346.69</v>
+      </c>
+      <c r="D446" t="n">
+        <v>342.39</v>
+      </c>
+      <c r="E446" t="n">
+        <v>350.61</v>
+      </c>
+      <c r="F446" t="n">
+        <v>345.33</v>
+      </c>
+      <c r="G446" t="n">
+        <v>343.92</v>
+      </c>
+      <c r="H446" t="n">
+        <v>344.58</v>
+      </c>
+      <c r="I446" t="n">
+        <v>342.54</v>
+      </c>
+      <c r="J446" t="n">
+        <v>342.91</v>
+      </c>
+      <c r="K446" t="n">
+        <v>344.19</v>
+      </c>
+      <c r="L446" t="n">
+        <v>343.97</v>
+      </c>
+      <c r="M446" t="n">
+        <v>341.64</v>
+      </c>
+      <c r="N446" t="n">
+        <v>347.37</v>
+      </c>
+      <c r="O446" t="n">
+        <v>339.84</v>
+      </c>
+      <c r="P446" t="n">
+        <v>335.09</v>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>390.2</v>
+      </c>
+      <c r="C447" t="n">
+        <v>341.62</v>
+      </c>
+      <c r="D447" t="n">
+        <v>337.23</v>
+      </c>
+      <c r="E447" t="n">
+        <v>346.45</v>
+      </c>
+      <c r="F447" t="n">
+        <v>342.39</v>
+      </c>
+      <c r="G447" t="n">
+        <v>341.46</v>
+      </c>
+      <c r="H447" t="n">
+        <v>342.37</v>
+      </c>
+      <c r="I447" t="n">
+        <v>337.05</v>
+      </c>
+      <c r="J447" t="n">
+        <v>337.76</v>
+      </c>
+      <c r="K447" t="n">
+        <v>338.12</v>
+      </c>
+      <c r="L447" t="n">
+        <v>339.48</v>
+      </c>
+      <c r="M447" t="n">
+        <v>336.31</v>
+      </c>
+      <c r="N447" t="n">
+        <v>347.37</v>
+      </c>
+      <c r="O447" t="n">
+        <v>334.92</v>
+      </c>
+      <c r="P447" t="n">
+        <v>329.94</v>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>389.48</v>
+      </c>
+      <c r="C448" t="n">
+        <v>336.88</v>
+      </c>
+      <c r="D448" t="n">
+        <v>332.11</v>
+      </c>
+      <c r="E448" t="n">
+        <v>342.16</v>
+      </c>
+      <c r="F448" t="n">
+        <v>338.74</v>
+      </c>
+      <c r="G448" t="n">
+        <v>338.79</v>
+      </c>
+      <c r="H448" t="n">
+        <v>341.97</v>
+      </c>
+      <c r="I448" t="n">
+        <v>331.26</v>
+      </c>
+      <c r="J448" t="n">
+        <v>330.78</v>
+      </c>
+      <c r="K448" t="n">
+        <v>331.94</v>
+      </c>
+      <c r="L448" t="n">
+        <v>333.92</v>
+      </c>
+      <c r="M448" t="n">
+        <v>335.04</v>
+      </c>
+      <c r="N448" t="n">
+        <v>345.6</v>
+      </c>
+      <c r="O448" t="n">
+        <v>333.59</v>
+      </c>
+      <c r="P448" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>388.47</v>
+      </c>
+      <c r="C449" t="n">
+        <v>333.05</v>
+      </c>
+      <c r="D449" t="n">
+        <v>327.87</v>
+      </c>
+      <c r="E449" t="n">
+        <v>337.71</v>
+      </c>
+      <c r="F449" t="n">
+        <v>334.49</v>
+      </c>
+      <c r="G449" t="n">
+        <v>335.61</v>
+      </c>
+      <c r="H449" t="n">
+        <v>339.13</v>
+      </c>
+      <c r="I449" t="n">
+        <v>331.26</v>
+      </c>
+      <c r="J449" t="n">
+        <v>330.78</v>
+      </c>
+      <c r="K449" t="n">
+        <v>326.68</v>
+      </c>
+      <c r="L449" t="n">
+        <v>328.69</v>
+      </c>
+      <c r="M449" t="n">
+        <v>333.14</v>
+      </c>
+      <c r="N449" t="n">
+        <v>342.34</v>
+      </c>
+      <c r="O449" t="n">
+        <v>331.67</v>
+      </c>
+      <c r="P449" t="n">
+        <v>324.05</v>
+      </c>
+      <c r="Q449" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25771,7 +25999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B520"/>
+  <dimension ref="A1:B525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30974,6 +31202,56 @@
       </c>
       <c r="B520" t="n">
         <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -31142,28 +31420,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2479093998000374</v>
+        <v>0.2512647702640042</v>
       </c>
       <c r="J2" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K2" t="n">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02720891256853142</v>
+        <v>0.02840150537494435</v>
       </c>
       <c r="M2" t="n">
-        <v>7.335771007537247</v>
+        <v>7.287225131533068</v>
       </c>
       <c r="N2" t="n">
-        <v>94.40495826654281</v>
+        <v>93.5791146888528</v>
       </c>
       <c r="O2" t="n">
-        <v>9.716221398596412</v>
+        <v>9.673629861063157</v>
       </c>
       <c r="P2" t="n">
-        <v>381.2028830385921</v>
+        <v>381.1594437756892</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31224,28 +31502,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1694695489243973</v>
+        <v>-0.1421638327715314</v>
       </c>
       <c r="J3" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K3" t="n">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009472652177566987</v>
+        <v>0.006696057751297779</v>
       </c>
       <c r="M3" t="n">
-        <v>9.094400302148676</v>
+        <v>9.146400447006595</v>
       </c>
       <c r="N3" t="n">
-        <v>128.8406967982501</v>
+        <v>129.7235151445117</v>
       </c>
       <c r="O3" t="n">
-        <v>11.35080159276208</v>
+        <v>11.3896231344374</v>
       </c>
       <c r="P3" t="n">
-        <v>329.7663077323488</v>
+        <v>329.4128544692054</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31302,28 +31580,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02251220307232516</v>
+        <v>0.04574256685923943</v>
       </c>
       <c r="J4" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K4" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001801051016170341</v>
+        <v>0.0007465696799621169</v>
       </c>
       <c r="M4" t="n">
-        <v>8.603152994151175</v>
+        <v>8.643185881289783</v>
       </c>
       <c r="N4" t="n">
-        <v>121.8173534646594</v>
+        <v>122.3153095396547</v>
       </c>
       <c r="O4" t="n">
-        <v>11.03708990018018</v>
+        <v>11.05962519887789</v>
       </c>
       <c r="P4" t="n">
-        <v>321.9825901614314</v>
+        <v>321.684051915605</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31380,28 +31658,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2103515423657865</v>
+        <v>0.2328721484926302</v>
       </c>
       <c r="J5" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K5" t="n">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01878320485768836</v>
+        <v>0.02298969293604658</v>
       </c>
       <c r="M5" t="n">
-        <v>8.059662743870868</v>
+        <v>8.088468604770259</v>
       </c>
       <c r="N5" t="n">
-        <v>101.3662198321104</v>
+        <v>101.9348532771396</v>
       </c>
       <c r="O5" t="n">
-        <v>10.06807925237532</v>
+        <v>10.09627917983351</v>
       </c>
       <c r="P5" t="n">
-        <v>326.5312092671405</v>
+        <v>326.2435599635444</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31458,28 +31736,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3445227759761889</v>
+        <v>0.3592668770547435</v>
       </c>
       <c r="J6" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K6" t="n">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05412667951072447</v>
+        <v>0.05912977646271145</v>
       </c>
       <c r="M6" t="n">
-        <v>7.701200709853221</v>
+        <v>7.704493599812471</v>
       </c>
       <c r="N6" t="n">
-        <v>90.96284550752621</v>
+        <v>90.84049083905063</v>
       </c>
       <c r="O6" t="n">
-        <v>9.537444390796006</v>
+        <v>9.531027795523977</v>
       </c>
       <c r="P6" t="n">
-        <v>323.1060409702259</v>
+        <v>322.9177278925078</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31536,28 +31814,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6287693200500141</v>
+        <v>0.6417113596988446</v>
       </c>
       <c r="J7" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K7" t="n">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1883892861169073</v>
+        <v>0.1963890310978942</v>
       </c>
       <c r="M7" t="n">
-        <v>6.914631913845724</v>
+        <v>6.91161439418255</v>
       </c>
       <c r="N7" t="n">
-        <v>74.69315906806344</v>
+        <v>74.52975790236471</v>
       </c>
       <c r="O7" t="n">
-        <v>8.642520411781707</v>
+        <v>8.633061907710653</v>
       </c>
       <c r="P7" t="n">
-        <v>316.161377334096</v>
+        <v>315.9960755693813</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31614,28 +31892,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8181438509710763</v>
+        <v>0.8304025146879581</v>
       </c>
       <c r="J8" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K8" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1941020568688703</v>
+        <v>0.2010621140626419</v>
       </c>
       <c r="M8" t="n">
-        <v>8.672779081644634</v>
+        <v>8.641503965264636</v>
       </c>
       <c r="N8" t="n">
-        <v>121.5487125240328</v>
+        <v>120.8672725851618</v>
       </c>
       <c r="O8" t="n">
-        <v>11.02491326605488</v>
+        <v>10.99396528033274</v>
       </c>
       <c r="P8" t="n">
-        <v>313.5405117631227</v>
+        <v>313.3836375295828</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31692,28 +31970,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3384094792143355</v>
+        <v>0.3612091497225027</v>
       </c>
       <c r="J9" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K9" t="n">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0201868678324314</v>
+        <v>0.02318986256670119</v>
       </c>
       <c r="M9" t="n">
-        <v>13.24050998221128</v>
+        <v>13.24888220378034</v>
       </c>
       <c r="N9" t="n">
-        <v>243.9786268501325</v>
+        <v>243.2943804660864</v>
       </c>
       <c r="O9" t="n">
-        <v>15.61981519897507</v>
+        <v>15.59789666801541</v>
       </c>
       <c r="P9" t="n">
-        <v>314.2377522330119</v>
+        <v>313.9466447077388</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31770,28 +32048,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09102740660659084</v>
+        <v>-0.06626288082114831</v>
       </c>
       <c r="J10" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K10" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001566658163098755</v>
+        <v>0.000839095916689514</v>
       </c>
       <c r="M10" t="n">
-        <v>12.15763733528371</v>
+        <v>12.16796409601822</v>
       </c>
       <c r="N10" t="n">
-        <v>229.4575996797502</v>
+        <v>229.1478543637625</v>
       </c>
       <c r="O10" t="n">
-        <v>15.14785792380395</v>
+        <v>15.13763040782019</v>
       </c>
       <c r="P10" t="n">
-        <v>324.8336752129368</v>
+        <v>324.5158831161353</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31848,28 +32126,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2058011941472183</v>
+        <v>-0.1721350621283819</v>
       </c>
       <c r="J11" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K11" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="L11" t="n">
-        <v>0.005837240006467459</v>
+        <v>0.004121423953025283</v>
       </c>
       <c r="M11" t="n">
-        <v>14.80901207442903</v>
+        <v>14.86787568050451</v>
       </c>
       <c r="N11" t="n">
-        <v>312.3367784959221</v>
+        <v>312.7031355910814</v>
       </c>
       <c r="O11" t="n">
-        <v>17.67305232538856</v>
+        <v>17.68341413842591</v>
       </c>
       <c r="P11" t="n">
-        <v>322.9034639897259</v>
+        <v>322.4707999763409</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31926,28 +32204,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.04607694589443075</v>
+        <v>-0.0199485747661517</v>
       </c>
       <c r="J12" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K12" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0004126514981743767</v>
+        <v>7.805340897681923e-05</v>
       </c>
       <c r="M12" t="n">
-        <v>12.50352073478986</v>
+        <v>12.52687243604594</v>
       </c>
       <c r="N12" t="n">
-        <v>222.6804549507441</v>
+        <v>222.6549868202788</v>
       </c>
       <c r="O12" t="n">
-        <v>14.92248152790762</v>
+        <v>14.92162815581057</v>
       </c>
       <c r="P12" t="n">
-        <v>323.9020061414553</v>
+        <v>323.5662213444773</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32004,28 +32282,28 @@
         <v>0.1389</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3631144081398365</v>
+        <v>-0.3400343151940933</v>
       </c>
       <c r="J13" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K13" t="n">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03384375677352991</v>
+        <v>0.03006009277102173</v>
       </c>
       <c r="M13" t="n">
-        <v>9.668431049279475</v>
+        <v>9.684349474886973</v>
       </c>
       <c r="N13" t="n">
-        <v>165.2145113284057</v>
+        <v>165.1591406373012</v>
       </c>
       <c r="O13" t="n">
-        <v>12.8535797087195</v>
+        <v>12.85142562664941</v>
       </c>
       <c r="P13" t="n">
-        <v>333.8895107979206</v>
+        <v>333.5948034008582</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32082,28 +32360,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4977898671701079</v>
+        <v>-0.4527936124770882</v>
       </c>
       <c r="J14" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K14" t="n">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06288378525365856</v>
+        <v>0.05191859194476556</v>
       </c>
       <c r="M14" t="n">
-        <v>9.997977882621111</v>
+        <v>10.15893778991624</v>
       </c>
       <c r="N14" t="n">
-        <v>162.0836872128351</v>
+        <v>165.7394589197733</v>
       </c>
       <c r="O14" t="n">
-        <v>12.73120918109647</v>
+        <v>12.87398380144131</v>
       </c>
       <c r="P14" t="n">
-        <v>334.8930913155332</v>
+        <v>334.3185025216989</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32160,28 +32438,28 @@
         <v>0.089</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2443384331761229</v>
+        <v>-0.2322617211666503</v>
       </c>
       <c r="J15" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K15" t="n">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02486014467353181</v>
+        <v>0.02280871313124666</v>
       </c>
       <c r="M15" t="n">
-        <v>7.878094314013512</v>
+        <v>7.869648511102038</v>
       </c>
       <c r="N15" t="n">
-        <v>102.7872511503044</v>
+        <v>102.314383537685</v>
       </c>
       <c r="O15" t="n">
-        <v>10.13840476358605</v>
+        <v>10.11505726813669</v>
       </c>
       <c r="P15" t="n">
-        <v>335.0757997313097</v>
+        <v>334.9216060537151</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32238,28 +32516,28 @@
         <v>0.035</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3376996656131883</v>
+        <v>-0.329492032008943</v>
       </c>
       <c r="J16" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="K16" t="n">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="L16" t="n">
-        <v>0.04740979894280339</v>
+        <v>0.04585958326678052</v>
       </c>
       <c r="M16" t="n">
-        <v>7.614072689403083</v>
+        <v>7.589998058593118</v>
       </c>
       <c r="N16" t="n">
-        <v>100.575380588188</v>
+        <v>99.99415874592023</v>
       </c>
       <c r="O16" t="n">
-        <v>10.02872776518477</v>
+        <v>9.999707933030855</v>
       </c>
       <c r="P16" t="n">
-        <v>333.6284758071542</v>
+        <v>333.5237033938257</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32297,7 +32575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q445"/>
+  <dimension ref="A1:Q449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70883,6 +71161,354 @@
         </is>
       </c>
     </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>-45.899097385675475,170.65226356218378</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>-45.8984126165515,170.65189431470165</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>-45.8980054928095,170.6512117200804</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-45.89769270219208,170.65043848838482</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>-45.89737452036448,170.6496977729997</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>-45.89715874703208,170.64886086554858</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>-45.89695819403825,170.6480098040708</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>-45.89673636162652,170.64717372345214</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>-45.89662647294582,170.64629655742235</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>-45.896548694594784,170.64540575941112</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>-45.896457280434426,170.6445171462826</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>-45.896347114590064,170.64363291705553</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>-45.89630571214555,170.64272920227936</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>-45.896113654605145,170.64186769404</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>-45.89594668010816,170.64100108407183</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>-45.899096820346514,170.6522642002061</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>-45.89837678886301,170.65193474891282</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>-45.897969029291666,170.6512528720365</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-45.89766147112183,170.65046802792077</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>-45.89735044720652,170.6497134700951</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>-45.897138005887236,170.64887192598385</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>-45.89693956078837,170.64801974063235</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>-45.89668890819585,170.64719335015192</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>-45.89658092749198,170.6463087450709</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>-45.896494815809206,170.64541852142588</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>-45.89641742617223,170.64452658680545</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>-45.896299817921104,170.64364424093702</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>-45.89630571214555,170.64272920227936</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>-45.89607047824185,170.64188166269992</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>-45.89590148542454,170.64101570616162</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>-45.899091732385685,170.65226994240638</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>-45.898343293140194,170.65197255126407</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>-45.89793284842087,170.6512937049315</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>-45.89762926407179,170.65049849053204</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>-45.89732056045929,170.64973295796634</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>-45.897115494155365,170.648883930593</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>-45.89693618825434,170.6480215391043</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>-45.896638861676756,170.6472140493111</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>-45.896519197922174,170.64632526344204</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>-45.89643996063462,170.6454315146853</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>-45.89636807434463,170.644538277054</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>-45.89628854835805,170.6436469391196</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>-45.89629008888115,170.64273361625163</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>-45.89605880658226,170.6418854387768</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>-45.89587436861308,170.64102447940346</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>-45.89908459510679,170.65227799743556</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>-45.8983162280209,170.65200309616844</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>-45.89790288612525,170.65132751963225</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>-45.89759585581691,170.6505300892403</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>-45.897285760817255,170.64975564929622</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>-45.89708868242778,170.6488982282043</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>-45.89691224326174,170.64803430824867</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>-45.896638861676756,170.6472140493111</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>-45.896519197922174,170.64632526344204</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>-45.8963932716006,170.64544257365128</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>-45.89632165167047,170.64454927343644</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>-45.89627168838164,170.64365097576848</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>-45.896261313828546,170.64274174593376</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>-45.89604195726884,170.6418908899525</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>-45.89584979674427,170.64103242925876</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
